--- a/data/input/dataframe.xlsx
+++ b/data/input/dataframe.xlsx
@@ -1,44 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DataFrame" sheetId="1" r:id="rId1"/>
+    <sheet name="DataFrame" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Source_One</t>
+    <t xml:space="preserve">Source_One</t>
   </si>
   <si>
-    <t>Source_Two</t>
+    <t xml:space="preserve">Source_Two</t>
   </si>
   <si>
-    <t>Source_Three</t>
+    <t xml:space="preserve">Source_Three</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.000;[Red]-#,##0.000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000;[RED]\-#,##0.000"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,7 +72,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -58,75 +80,132 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+  <cellXfs count="4">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.000;[Red]-#,##0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:C46" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:C46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:C46"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Source_One" dataDxfId="0"/>
-    <tableColumn id="2" name="Source_Two" dataDxfId="0"/>
-    <tableColumn id="3" name="Source_Three" dataDxfId="0"/>
+    <tableColumn id="1" name="Source_One"/>
+    <tableColumn id="2" name="Source_Two"/>
+    <tableColumn id="3" name="Source_Three"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -134,760 +213,782 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="n">
         <v>0.823</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2" t="n">
         <v>-0.025</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2" t="n">
         <v>0.991</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2" t="n">
         <v>-0.051</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
         <v>0.058</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2" t="n">
         <v>0.024</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
         <v>0.86</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2" t="n">
         <v>0.781</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2" t="n">
         <v>0.011</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
         <v>-0.168</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2" t="n">
         <v>0.986</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
         <v>-0.992</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2" t="n">
         <v>-0.026</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2" t="n">
         <v>-0.993</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="2" t="n">
         <v>-0.026</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
         <v>-0.032</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="2" t="n">
         <v>-0.081</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="2" t="n">
         <v>0.976</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
         <v>0.11</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2" t="n">
         <v>0.864</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="2" t="n">
         <v>0.21</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
         <v>-0.028</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="2" t="n">
         <v>0.043</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="2" t="n">
         <v>-0.021</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2" t="n">
         <v>-0.969</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="n">
         <v>0.988</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2" t="n">
         <v>0.899</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="2" t="n">
         <v>0.003</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
         <v>0.243</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="2" t="n">
         <v>-0.192</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="2" t="n">
         <v>0.001</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="2" t="n">
         <v>-0.96</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="2" t="n">
         <v>-0.984</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="n">
         <v>-0.948</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="2" t="n">
         <v>0.297</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="n">
         <v>-0.968</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="2" t="n">
         <v>0.08</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="2" t="n">
         <v>-0.04</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
         <v>-0.284</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
         <v>0.001</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="2" t="n">
         <v>0.004</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="2" t="n">
         <v>-0.964</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="1">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="n">
         <v>0.954</v>
       </c>
-      <c r="B22" s="1">
-        <v>0.9320000000000001</v>
-      </c>
-      <c r="C22" s="1">
+      <c r="B22" s="2" t="n">
+        <v>0.932</v>
+      </c>
+      <c r="C22" s="2" t="n">
         <v>0.898</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="1">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="n">
         <v>0.955</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="2" t="n">
         <v>0.013</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="2" t="n">
         <v>0.003</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="1">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="n">
         <v>0.926</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="2" t="n">
         <v>-0.944</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="2" t="n">
         <v>-0.002</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="1">
-        <v>-0.9419999999999999</v>
-      </c>
-      <c r="B25" s="1">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="n">
+        <v>-0.942</v>
+      </c>
+      <c r="B25" s="2" t="n">
         <v>0.016</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="2" t="n">
         <v>-0.963</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="n">
         <v>-0.22</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="2" t="n">
         <v>0.191</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="2" t="n">
         <v>-0.219</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="1">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="n">
         <v>0.235</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="2" t="n">
         <v>0.186</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="2" t="n">
         <v>0.179</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="1">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="n">
         <v>0.208</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="2" t="n">
         <v>0.202</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="2" t="n">
         <v>0.209</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="n">
         <v>0.202</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="2" t="n">
         <v>0.204</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="2" t="n">
         <v>0.201</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="1">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="n">
         <v>0.205</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="2" t="n">
         <v>0.206</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="2" t="n">
         <v>0.202</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="1">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="n">
         <v>0.206</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="2" t="n">
         <v>0.208</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="2" t="n">
         <v>0.203</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="1">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="n">
         <v>-0.999</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="2" t="n">
         <v>-0.999</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="2" t="n">
         <v>-0.999</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="1">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="n">
         <v>0.912</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="2" t="n">
         <v>-0.981</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="2" t="n">
         <v>-0.925</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="1">
-        <v>-0.9419999999999999</v>
-      </c>
-      <c r="B34" s="1">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="n">
+        <v>-0.942</v>
+      </c>
+      <c r="B34" s="2" t="n">
         <v>-0.952</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="2" t="n">
         <v>-0.946</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0.9419999999999999</v>
-      </c>
-      <c r="C35" s="1">
-        <v>-0.9429999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="n">
+        <v>0.941</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0.942</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>-0.943</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="n">
         <v>-0.012</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="2" t="n">
         <v>-0.983</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="2" t="n">
         <v>-0.021</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="1">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="2" t="n">
         <v>-0.954</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="2" t="n">
         <v>-0.014</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="1">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="n">
         <v>0.001</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="2" t="n">
         <v>-0.972</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="2" t="n">
         <v>-0.029</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="1">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="n">
         <v>0.012</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="2" t="n">
         <v>-0.897</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="2" t="n">
         <v>-0.021</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="B40" s="1">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="B40" s="2" t="n">
         <v>-0.904</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="2" t="n">
         <v>0.014</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="1">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="n">
         <v>-0.021</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="2" t="n">
         <v>-0.999</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="1">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="n">
         <v>-0.014</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="2" t="n">
         <v>0.001</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="2" t="n">
         <v>-0.925</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="n">
         <v>-0.029</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="2" t="n">
         <v>0.012</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="2" t="n">
         <v>-0.946</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="1">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="n">
         <v>-0.003</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="2" t="n">
         <v>0.951</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="2" t="n">
         <v>-0.958</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="n">
         <v>0.014</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="2" t="n">
         <v>0.906</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="2" t="n">
         <v>-0.895</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="2" t="n">
         <v>0.949</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="2" t="n">
         <v>-0.925</v>
       </c>
     </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>-0.925</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>-0.964</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>-0.964</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>-0.944</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="n">
+        <v>0.933</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>-0.922</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>-0.911</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>-0.994</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>-0.953</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="n">
+        <v>0.942</v>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>0.967</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>0.965</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>-0.894</v>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>-0.921</v>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>0.912</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C55" s="0" t="n">
+        <v>0.923</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="C56" s="0" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>-0.913</v>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>-0.005</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>

--- a/data/input/dataframe.xlsx
+++ b/data/input/dataframe.xlsx
@@ -350,7 +350,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -904,80 +904,168 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+      <c r="A51" s="3" t="n">
         <v>0.942</v>
       </c>
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="3" t="n">
         <v>0.888</v>
       </c>
-      <c r="C51" s="0" t="n">
+      <c r="C51" s="3" t="n">
         <v>0.967</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
+      <c r="A52" s="3" t="n">
         <v>0.879</v>
       </c>
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="3" t="n">
         <v>0.944</v>
       </c>
-      <c r="C52" s="0" t="n">
+      <c r="C52" s="3" t="n">
         <v>0.965</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="n">
+      <c r="A53" s="3" t="n">
         <v>0.891</v>
       </c>
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="3" t="n">
         <v>-0.894</v>
       </c>
-      <c r="C53" s="0" t="n">
+      <c r="C53" s="3" t="n">
         <v>0.999</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="n">
+      <c r="A54" s="3" t="n">
         <v>0.965</v>
       </c>
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="3" t="n">
         <v>-0.921</v>
       </c>
-      <c r="C54" s="0" t="n">
+      <c r="C54" s="3" t="n">
         <v>0.912</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="n">
+      <c r="A55" s="3" t="n">
         <v>0.911</v>
       </c>
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="3" t="n">
         <v>0.001</v>
       </c>
-      <c r="C55" s="0" t="n">
+      <c r="C55" s="3" t="n">
         <v>0.923</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="n">
+      <c r="A56" s="3" t="n">
         <v>0.002</v>
       </c>
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="3" t="n">
         <v>0.912</v>
       </c>
-      <c r="C56" s="0" t="n">
+      <c r="C56" s="3" t="n">
         <v>0.003</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="n">
+      <c r="A57" s="3" t="n">
         <v>0.004</v>
       </c>
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="3" t="n">
         <v>-0.913</v>
       </c>
-      <c r="C57" s="0" t="n">
+      <c r="C57" s="3" t="n">
         <v>-0.005</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="n">
+        <v>-0.992</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>0.943</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>-0.954</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>-0.091</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="n">
+        <v>-0.894</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>-0.081</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="n">
+        <v>-0.984</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>-0.994</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>-0.894</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>-0.905</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>-0.991</v>
+      </c>
+      <c r="C65" s="0" t="n">
+        <v>0.041</v>
       </c>
     </row>
   </sheetData>
